--- a/employment_forms/013_employee_nomination_form--employment_forms.xlsx
+++ b/employment_forms/013_employee_nomination_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employee_1',_'label':_'employee_1'}</t>
+          <t>employee_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'employee_1', 'label': 'Employee 1'}</t>
+          <t>Employee 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'employee_2',_'label':_'employee_2'}</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'employee_2', 'label': 'Employee 2'}</t>
+          <t>Employee 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'employee_3',_'label':_'employee_3'}</t>
+          <t>employee_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'employee_3', 'label': 'Employee 3'}</t>
+          <t>Employee 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'employee_4',_'label':_'employee_4'}</t>
+          <t>employee_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'employee_4', 'label': 'Employee 4'}</t>
+          <t>Employee 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'employee_5',_'label':_'employee_5'}</t>
+          <t>employee_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'employee_5', 'label': 'Employee 5'}</t>
+          <t>Employee 5</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_time',_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'full_time', 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part_time',_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'part_time', 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract',_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contract', 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'on_loan',_'label':_'on_loan'}</t>
+          <t>on_loan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'on_loan', 'label': 'On Loan'}</t>
+          <t>On Loan</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'resigned',_'label':_'resigned'}</t>
+          <t>resigned</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'resigned', 'label': 'Resigned'}</t>
+          <t>Resigned</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_time',_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'full_time', 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part_time',_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'part_time', 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract',_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contract', 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'temporary',_'label':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'temporary', 'label': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'seasonal',_'label':_'seasonal'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'seasonal', 'label': 'Seasonal'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'internship',_'label':_'internship'}</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'internship', 'label': 'Internship'}</t>
+          <t>Internship</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'co_op',_'label':_'co-op'}</t>
+          <t>co-op</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'co_op', 'label': 'Co-Op'}</t>
+          <t>Co-Op</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager_1',_'label':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'manager_1', 'label': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'manager_2',_'label':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'manager_2', 'label': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'manager_3',_'label':_'manager_3'}</t>
+          <t>manager_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'manager_3', 'label': 'Manager 3'}</t>
+          <t>Manager 3</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'manager_4',_'label':_'manager_4'}</t>
+          <t>manager_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'manager_4', 'label': 'Manager 4'}</t>
+          <t>Manager 4</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'manager_5',_'label':_'manager_5'}</t>
+          <t>manager_5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'manager_5', 'label': 'Manager 5'}</t>
+          <t>Manager 5</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'manager_6',_'label':_'manager_6'}</t>
+          <t>manager_6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'manager_6', 'label': 'Manager 6'}</t>
+          <t>Manager 6</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'supervisor_1',_'label':_'supervisor_1'}</t>
+          <t>supervisor_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'supervisor_1', 'label': 'Supervisor 1'}</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supervisor_2',_'label':_'supervisor_2'}</t>
+          <t>supervisor_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'supervisor_2', 'label': 'Supervisor 2'}</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'supervisor_3',_'label':_'supervisor_3'}</t>
+          <t>supervisor_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'supervisor_3', 'label': 'Supervisor 3'}</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'supervisor_4',_'label':_'supervisor_4'}</t>
+          <t>supervisor_4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'supervisor_4', 'label': 'Supervisor 4'}</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'supervisor_5',_'label':_'supervisor_5'}</t>
+          <t>supervisor_5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'supervisor_5', 'label': 'Supervisor 5'}</t>
+          <t>Supervisor 5</t>
         </is>
       </c>
     </row>
